--- a/Torneo_Volta_LaLiga_25_26.xlsx
+++ b/Torneo_Volta_LaLiga_25_26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2015b\Documents\GitHub\Pavel775.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4396704-D828-4B42-85B5-9D521792BBB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE03D258-49F3-4714-857A-7B3E782DD017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
   <si>
     <t>Equipo</t>
   </si>
@@ -156,269 +156,6 @@
     <t>Jornada 1</t>
   </si>
   <si>
-    <r>
-      <t>Real Madrid CF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Valencia CF</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>FC Barcelona</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sevilla FC</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Atlético de Madrid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Real Sociedad</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Athletic Club</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Villarreal CF</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Real Betis</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Girona FC</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Rayo Vallecano</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Celta de Vigo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>CA Osasuna</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Getafe CF</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>RCD Mallorca</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Deportivo Alavés</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Levante UD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Elche CF</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>RCD Espanyol</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Real Oviedo</t>
-    </r>
-  </si>
-  <si>
-    <t>1-0</t>
-  </si>
-  <si>
     <t>3-0</t>
   </si>
   <si>
@@ -426,6 +163,78 @@
   </si>
   <si>
     <t>0-1</t>
+  </si>
+  <si>
+    <t>Real Madrid CF vs Villarreal CF</t>
+  </si>
+  <si>
+    <t>Valencia CF vs Real Betis</t>
+  </si>
+  <si>
+    <t>Sevilla FC vs RCD Mallorca</t>
+  </si>
+  <si>
+    <t>Real Sociedad vs Athletic Club</t>
+  </si>
+  <si>
+    <t>RCD Espanyol vs Atlético de Madrid</t>
+  </si>
+  <si>
+    <t>Rayo Vallecano vs Girona FC</t>
+  </si>
+  <si>
+    <t>Celta de Vigo vs CA Osasuna</t>
+  </si>
+  <si>
+    <t>Deportivo Alavés vs Real Oviedo</t>
+  </si>
+  <si>
+    <t>Elche CF vs Levante UD</t>
+  </si>
+  <si>
+    <t>FC Barcelona vs Getafe CF</t>
+  </si>
+  <si>
+    <t>Real Madrid CF vs Valencia CF</t>
+  </si>
+  <si>
+    <t>FC Barcelona vs Sevilla FC</t>
+  </si>
+  <si>
+    <t>Atlético de Madrid vs Real Sociedad</t>
+  </si>
+  <si>
+    <t>Villarreal CF vs Real Betis</t>
+  </si>
+  <si>
+    <t>Athletic Club vs RCD Mallorca</t>
+  </si>
+  <si>
+    <t>Girona FC vs Rayo Vallecano</t>
+  </si>
+  <si>
+    <t>Getafe CF vs Celta de Vigo</t>
+  </si>
+  <si>
+    <t>Levante UD vs RCD Espanyol</t>
+  </si>
+  <si>
+    <t>CA Osasuna vs Deportivo Alavés</t>
+  </si>
+  <si>
+    <t>Real Oviedo vs Elche CF</t>
+  </si>
+  <si>
+    <t>0-0</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>1-1</t>
   </si>
 </sst>
 </file>
@@ -435,7 +244,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,6 +275,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -488,7 +303,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -500,9 +315,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -564,6 +383,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E069EC19-FAC0-4695-BF7F-0AE162123DBC}" name="Tabla1" displayName="Tabla1" ref="A1:F21" totalsRowShown="0" dataDxfId="12">
   <autoFilter ref="A1:F21" xr:uid="{E069EC19-FAC0-4695-BF7F-0AE162123DBC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F21">
+    <sortCondition descending="1" ref="A1:A21"/>
+  </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{A20ADE9B-DFE4-4EB9-AFCD-05203C7BEDE1}" name="Equipo" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{30C2E249-8CA9-4FF5-BDF7-BFD96B2B05C5}" name="PJ" dataDxfId="10"/>
@@ -902,7 +724,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -922,10 +744,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1">
         <v>0</v>
@@ -934,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -942,10 +764,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -954,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -962,7 +784,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
@@ -982,7 +804,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1">
         <v>0</v>
@@ -1002,13 +824,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -1017,18 +839,18 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -1042,7 +864,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1">
         <v>0</v>
@@ -1062,7 +884,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
@@ -1082,7 +904,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
@@ -1102,7 +924,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1">
         <v>0</v>
@@ -1122,7 +944,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1">
         <v>0</v>
@@ -1142,7 +964,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>
@@ -1162,13 +984,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -1182,13 +1004,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -1197,12 +1019,12 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B17" s="1">
         <v>0</v>
@@ -1223,7 +1045,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
@@ -1243,10 +1065,10 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" s="1">
         <v>0</v>
@@ -1255,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1266,10 +1088,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="1">
         <v>0</v>
@@ -1278,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1286,7 +1108,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B21" s="1">
         <v>0</v>
@@ -1314,123 +1136,181 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CD23420-640D-43B7-A025-C07EFD6C184C}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="1"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="1"/>
+      <c r="D11" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C12" s="4"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C14" s="4"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="4"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="4"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="4"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
